--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2762-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2762-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{282AD606-CA51-4BDC-B799-6133199B26D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61733995-7660-43ED-92D1-0E386838AB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{1A4FCDFC-A449-40DA-96E0-2522FFA3FCB8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F5D91547-AD58-4B26-B9E4-AD0A8B7FD1DE}"/>
   </bookViews>
   <sheets>
     <sheet name="2762-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1513,21 +1513,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37583C90-8C74-4B86-8041-A630571E6E3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5B7627-EB16-4445-A192-8F22E3DCA10F}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1555,7 +1555,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1585,7 +1585,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1681,7 +1681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1761,7 +1761,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="49" t="s">
         <v>42</v>
       </c>
